--- a/Team-Data/2013-14/11-30-2013-14.xlsx
+++ b/Team-Data/2013-14/11-30-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
@@ -679,64 +746,64 @@
         <v>36.8</v>
       </c>
       <c r="J2" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
         <v>7.7</v>
       </c>
       <c r="M2" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O2" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P2" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.746</v>
+        <v>0.739</v>
       </c>
       <c r="R2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T2" t="n">
         <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
         <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="AD2" t="n">
         <v>2</v>
@@ -745,10 +812,10 @@
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
@@ -757,19 +824,19 @@
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
         <v>9</v>
       </c>
       <c r="AL2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN2" t="n">
         <v>15</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>14</v>
@@ -778,7 +845,7 @@
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -793,7 +860,7 @@
         <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -805,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -843,49 +910,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.368</v>
+        <v>0.389</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J3" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M3" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="O3" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="P3" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R3" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
         <v>30.9</v>
@@ -897,40 +964,40 @@
         <v>17.8</v>
       </c>
       <c r="V3" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="W3" t="n">
         <v>7.3</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>22</v>
@@ -942,7 +1009,7 @@
         <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -951,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
@@ -966,31 +1033,31 @@
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU3" t="n">
         <v>29</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>0.294</v>
+        <v>0.25</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,19 +1110,19 @@
         <v>34.8</v>
       </c>
       <c r="J4" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.36</v>
+        <v>0.351</v>
       </c>
       <c r="O4" t="n">
         <v>19.5</v>
@@ -1064,64 +1131,64 @@
         <v>25.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R4" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
         <v>31.3</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V4" t="n">
         <v>15</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
         <v>4.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6.6</v>
+        <v>-7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH4" t="n">
         <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1133,7 +1200,7 @@
         <v>24</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
@@ -1148,7 +1215,7 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
         <v>19</v>
@@ -1163,13 +1230,13 @@
         <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>16</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>7</v>
@@ -1330,13 +1397,13 @@
         <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>6</v>
@@ -1348,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>0.427</v>
       </c>
       <c r="L6" t="n">
         <v>4.9</v>
@@ -1419,34 +1486,34 @@
         <v>14.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.332</v>
+        <v>0.327</v>
       </c>
       <c r="O6" t="n">
-        <v>17.7</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.793</v>
+        <v>0.803</v>
       </c>
       <c r="R6" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>33.3</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>45.8</v>
+        <v>46.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="V6" t="n">
-        <v>16.5</v>
+        <v>16.9</v>
       </c>
       <c r="W6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X6" t="n">
         <v>4.1</v>
@@ -1455,34 +1522,34 @@
         <v>6.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
         <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
         <v>22</v>
@@ -1497,28 +1564,28 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
         <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
         <v>22</v>
@@ -1536,13 +1603,13 @@
         <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -1571,49 +1638,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.294</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
         <v>48.9</v>
       </c>
       <c r="I7" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J7" t="n">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.419</v>
+        <v>0.415</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>0.349</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
         <v>15.7</v>
       </c>
       <c r="P7" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.754</v>
+        <v>0.749</v>
       </c>
       <c r="R7" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S7" t="n">
         <v>30.9</v>
@@ -1622,43 +1689,43 @@
         <v>42.1</v>
       </c>
       <c r="U7" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="V7" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="W7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-8.4</v>
+        <v>-9.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH7" t="n">
         <v>4</v>
@@ -1667,7 +1734,7 @@
         <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK7" t="n">
         <v>28</v>
@@ -1676,52 +1743,52 @@
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV7" t="n">
         <v>23</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -1753,82 +1820,82 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>0.556</v>
+        <v>0.588</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M8" t="n">
         <v>23.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.382</v>
+        <v>0.388</v>
       </c>
       <c r="O8" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="P8" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0.8169999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="W8" t="n">
         <v>9.4</v>
       </c>
       <c r="X8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
         <v>2</v>
@@ -1846,67 +1913,67 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM8" t="n">
         <v>8</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS8" t="n">
         <v>20</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>23</v>
       </c>
       <c r="AT8" t="n">
         <v>23</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>9</v>
@@ -2028,7 +2095,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
@@ -2043,7 +2110,7 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2052,16 +2119,16 @@
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>14</v>
@@ -2085,10 +2152,10 @@
         <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,7 +2271,7 @@
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>14</v>
@@ -2213,13 +2280,13 @@
         <v>11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
         <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
         <v>22</v>
@@ -2243,13 +2310,13 @@
         <v>29</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
@@ -2258,13 +2325,13 @@
         <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
         <v>10</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>9</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
@@ -2416,7 +2483,7 @@
         <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
         <v>26</v>
@@ -2431,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>19</v>
@@ -2443,10 +2510,10 @@
         <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -2481,88 +2548,88 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.722</v>
+        <v>0.706</v>
       </c>
       <c r="H12" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
-        <v>77.5</v>
+        <v>76.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.489</v>
+        <v>0.492</v>
       </c>
       <c r="L12" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="M12" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.381</v>
+        <v>0.378</v>
       </c>
       <c r="O12" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="P12" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.704</v>
+        <v>0.707</v>
       </c>
       <c r="R12" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S12" t="n">
-        <v>35.9</v>
+        <v>35.5</v>
       </c>
       <c r="T12" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="U12" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V12" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="W12" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>25.7</v>
+        <v>26.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>109.4</v>
+        <v>109.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
@@ -2574,7 +2641,7 @@
         <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ12" t="n">
         <v>29</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
         <v>15</v>
@@ -2616,16 +2683,16 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>11.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2780,7 +2847,7 @@
         <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR13" t="n">
         <v>24</v>
@@ -2789,7 +2856,7 @@
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>21</v>
@@ -2798,13 +2865,13 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2990,19 @@
         <v>5.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2980,13 +3047,13 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ14" t="n">
         <v>29</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -3105,22 +3172,22 @@
         <v>-1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>9</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>3</v>
@@ -3141,7 +3208,7 @@
         <v>27</v>
       </c>
       <c r="AP15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3156,7 +3223,7 @@
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -3209,94 +3276,94 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H16" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I16" t="n">
         <v>36.6</v>
       </c>
       <c r="J16" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M16" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.324</v>
+        <v>0.314</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="P16" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R16" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>30.9</v>
+        <v>31.2</v>
       </c>
       <c r="T16" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="U16" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V16" t="n">
         <v>14.3</v>
       </c>
       <c r="W16" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>7</v>
@@ -3317,25 +3384,25 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR16" t="n">
         <v>21</v>
       </c>
-      <c r="AP16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>25</v>
-      </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
@@ -3344,25 +3411,25 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
@@ -3523,22 +3590,22 @@
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -3573,88 +3640,88 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.188</v>
+        <v>0.133</v>
       </c>
       <c r="H18" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="J18" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.415</v>
+        <v>0.412</v>
       </c>
       <c r="L18" t="n">
         <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.382</v>
+        <v>0.377</v>
       </c>
       <c r="O18" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="P18" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.774</v>
+        <v>0.786</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>28.9</v>
       </c>
       <c r="T18" t="n">
-        <v>39.9</v>
+        <v>39.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="W18" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.6</v>
+        <v>-10.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,34 +3757,34 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR18" t="n">
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>29</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J19" t="n">
-        <v>89.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.431</v>
+        <v>0.427</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M19" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.329</v>
+        <v>0.323</v>
       </c>
       <c r="O19" t="n">
         <v>21.1</v>
       </c>
       <c r="P19" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S19" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="T19" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
@@ -3812,22 +3879,22 @@
         <v>14.7</v>
       </c>
       <c r="W19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X19" t="n">
         <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.1</v>
+        <v>105.7</v>
       </c>
       <c r="AC19" t="n">
         <v>4.8</v>
@@ -3836,16 +3903,16 @@
         <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
         <v>16</v>
       </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>8</v>
@@ -3854,43 +3921,43 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AM19" t="n">
         <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR19" t="n">
         <v>3</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>18</v>
@@ -4048,7 +4115,7 @@
         <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP20" t="n">
         <v>15</v>
@@ -4057,16 +4124,16 @@
         <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4078,19 +4145,19 @@
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ20" t="n">
         <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
         <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-6.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
         <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>23</v>
@@ -4221,13 +4288,13 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM21" t="n">
         <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4242,34 +4309,34 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
         <v>13</v>
       </c>
       <c r="AZ21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
         <v>27</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>4.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
         <v>5</v>
@@ -4409,16 +4476,16 @@
         <v>23</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR22" t="n">
         <v>11</v>
@@ -4430,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
@@ -4570,7 +4637,7 @@
         <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH23" t="n">
         <v>14</v>
@@ -4582,25 +4649,25 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL23" t="n">
         <v>12</v>
       </c>
       <c r="AM23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP23" t="n">
         <v>24</v>
       </c>
-      <c r="AP23" t="n">
-        <v>23</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4609,19 +4676,19 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU23" t="n">
         <v>16</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX23" t="n">
         <v>17</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>18</v>
       </c>
       <c r="AY23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4755,7 +4822,7 @@
         <v>24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI24" t="n">
         <v>2</v>
@@ -4773,10 +4840,10 @@
         <v>11</v>
       </c>
       <c r="AN24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4800,7 +4867,7 @@
         <v>29</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX24" t="n">
         <v>14</v>
@@ -4812,7 +4879,7 @@
         <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -4847,85 +4914,85 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
         <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>0.529</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J25" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M25" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.368</v>
+        <v>0.363</v>
       </c>
       <c r="O25" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P25" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S25" t="n">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="T25" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="V25" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W25" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>101.7</v>
+        <v>101.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4937,10 +5004,10 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ25" t="n">
         <v>20</v>
@@ -4961,40 +5028,40 @@
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU25" t="n">
         <v>26</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG26" t="n">
         <v>3</v>
@@ -5122,7 +5189,7 @@
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
         <v>6</v>
@@ -5146,7 +5213,7 @@
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
         <v>6</v>
@@ -5158,7 +5225,7 @@
         <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>4</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
         <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
@@ -5307,25 +5374,25 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
       </c>
       <c r="AM27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>15</v>
       </c>
       <c r="AP27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
         <v>10</v>
@@ -5337,16 +5404,16 @@
         <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV27" t="n">
         <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX27" t="n">
         <v>30</v>
@@ -5358,7 +5425,7 @@
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
         <v>21</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -5393,58 +5460,58 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
         <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>0.824</v>
+        <v>0.875</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="J28" t="n">
-        <v>83.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.488</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.396</v>
       </c>
       <c r="O28" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="P28" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="R28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="S28" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="T28" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="U28" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5453,25 +5520,25 @@
         <v>8.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
         <v>17.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5498,7 +5565,7 @@
         <v>10</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
         <v>6</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5519,19 +5586,19 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>0.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
         <v>20</v>
@@ -5671,10 +5738,10 @@
         <v>26</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
         <v>18</v>
@@ -5683,13 +5750,13 @@
         <v>14</v>
       </c>
       <c r="AN29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
         <v>5</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>12</v>
@@ -5707,19 +5774,19 @@
         <v>30</v>
       </c>
       <c r="AV29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>21</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -5728,7 +5795,7 @@
         <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -5757,88 +5824,88 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>0.167</v>
+        <v>0.118</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.426</v>
+        <v>0.421</v>
       </c>
       <c r="L30" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="M30" t="n">
         <v>18.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.308</v>
+        <v>0.297</v>
       </c>
       <c r="O30" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="P30" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.715</v>
+        <v>0.704</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T30" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U30" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V30" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="W30" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>90.5</v>
+        <v>89.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.7</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF30" t="n">
         <v>30</v>
@@ -5847,34 +5914,34 @@
         <v>30</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>28</v>
       </c>
       <c r="AJ30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK30" t="n">
         <v>26</v>
       </c>
-      <c r="AK30" t="n">
-        <v>25</v>
-      </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AP30" t="n">
         <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
@@ -5883,28 +5950,28 @@
         <v>30</v>
       </c>
       <c r="AT30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV30" t="n">
         <v>27</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>26</v>
       </c>
       <c r="AW30" t="n">
         <v>18</v>
       </c>
       <c r="AX30" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
@@ -5939,55 +6006,55 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>0.471</v>
+        <v>0.438</v>
       </c>
       <c r="H31" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="I31" t="n">
         <v>37.6</v>
       </c>
       <c r="J31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N31" t="n">
-        <v>0.39</v>
+        <v>0.383</v>
       </c>
       <c r="O31" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="P31" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.734</v>
+        <v>0.741</v>
       </c>
       <c r="R31" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="S31" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T31" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U31" t="n">
         <v>23.9</v>
@@ -5996,37 +6063,37 @@
         <v>15.6</v>
       </c>
       <c r="W31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="X31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.7</v>
+        <v>-2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
@@ -6035,64 +6102,64 @@
         <v>16</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM31" t="n">
         <v>9</v>
       </c>
       <c r="AN31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
       </c>
       <c r="AP31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT31" t="n">
         <v>25</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>23</v>
       </c>
       <c r="AU31" t="n">
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
       </c>
       <c r="BC31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-30-2013-14</t>
+          <t>2013-11-30</t>
         </is>
       </c>
     </row>
